--- a/other/cols_hbsc2018.xlsx
+++ b/other/cols_hbsc2018.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MisLocalFiles\Github\HBSC\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{A181C51E-36AA-4690-B0ED-35CCD84C1DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30220D21-588B-4A95-9DEB-A0E43A456537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6075EEDB-BE57-4BE5-AE0A-AA8F7DB9F88A}"/>
   </bookViews>
@@ -20,12 +20,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">varsCategorized!$A$1:$E$121</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="496">
   <si>
     <t>HBSC</t>
   </si>
@@ -1510,6 +1523,9 @@
   </si>
   <si>
     <t>country code/name</t>
+  </si>
+  <si>
+    <t>WalterCategory</t>
   </si>
 </sst>
 </file>
@@ -2083,7 +2099,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2097,8 +2113,6 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1"/>
@@ -2492,7 +2506,7 @@
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
     <col min="2" max="2" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
     <col min="5" max="5" width="103" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2506,8 +2520,8 @@
       <c r="C1" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>121</v>
+      <c r="D1" s="4" t="s">
+        <v>495</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>359</v>
@@ -2518,11 +2532,11 @@
         <v>222</v>
       </c>
       <c r="B2" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A2, " "))</f>
+        <f t="shared" ref="B2:B33" si="0">INT(_xlfn.TEXTBEFORE(A2, " "))</f>
         <v>65</v>
       </c>
       <c r="C2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2, " "), " ")</f>
+        <f t="shared" ref="C2:C33" si="1">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2, " "), " ")</f>
         <v>bulliedo</v>
       </c>
       <c r="D2" s="6" t="s">
@@ -2537,11 +2551,11 @@
         <v>225</v>
       </c>
       <c r="B3" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A3, " "))</f>
+        <f t="shared" si="0"/>
         <v>66</v>
       </c>
       <c r="C3" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>beenbull</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -2556,11 +2570,11 @@
         <v>227</v>
       </c>
       <c r="B4" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A4, " "))</f>
+        <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="C4" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>cbullied</v>
       </c>
       <c r="D4" s="6" t="s">
@@ -2575,11 +2589,11 @@
         <v>235</v>
       </c>
       <c r="B5" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A5, " "))</f>
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="C5" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A5, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>cbeenbul</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -2594,11 +2608,11 @@
         <v>236</v>
       </c>
       <c r="B6" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A6, " "))</f>
+        <f t="shared" si="0"/>
         <v>69</v>
       </c>
       <c r="C6" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A6, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>fight12m</v>
       </c>
       <c r="D6" s="6" t="s">
@@ -2613,11 +2627,11 @@
         <v>321</v>
       </c>
       <c r="B7" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A7, " "))</f>
+        <f t="shared" si="0"/>
         <v>98</v>
       </c>
       <c r="C7" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A7, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>motherho</v>
       </c>
       <c r="D7" s="10" t="s">
@@ -2632,11 +2646,11 @@
         <v>322</v>
       </c>
       <c r="B8" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A8, " "))</f>
+        <f t="shared" si="0"/>
         <v>99</v>
       </c>
       <c r="C8" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A8, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>fatherho</v>
       </c>
       <c r="D8" s="10" t="s">
@@ -2651,11 +2665,11 @@
         <v>323</v>
       </c>
       <c r="B9" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A9, " "))</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="C9" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A9, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>stepmoho</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -2670,11 +2684,11 @@
         <v>324</v>
       </c>
       <c r="B10" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A10, " "))</f>
+        <f t="shared" si="0"/>
         <v>101</v>
       </c>
       <c r="C10" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A10, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>stepfaho</v>
       </c>
       <c r="D10" s="10" t="s">
@@ -2689,11 +2703,11 @@
         <v>325</v>
       </c>
       <c r="B11" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A11, " "))</f>
+        <f t="shared" si="0"/>
         <v>102</v>
       </c>
       <c r="C11" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A11, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>fosterho</v>
       </c>
       <c r="D11" s="10" t="s">
@@ -2708,11 +2722,11 @@
         <v>326</v>
       </c>
       <c r="B12" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A12, " "))</f>
+        <f t="shared" si="0"/>
         <v>103</v>
       </c>
       <c r="C12" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A12, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>elsehome</v>
       </c>
       <c r="D12" s="10" t="s">
@@ -2727,11 +2741,11 @@
         <v>329</v>
       </c>
       <c r="B13" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A13, " "))</f>
+        <f t="shared" si="0"/>
         <v>104</v>
       </c>
       <c r="C13" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A13, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>employfa</v>
       </c>
       <c r="D13" s="10" t="s">
@@ -2746,11 +2760,11 @@
         <v>330</v>
       </c>
       <c r="B14" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A14, " "))</f>
+        <f t="shared" si="0"/>
         <v>105</v>
       </c>
       <c r="C14" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A14, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>employmo</v>
       </c>
       <c r="D14" s="10" t="s">
@@ -2765,11 +2779,11 @@
         <v>331</v>
       </c>
       <c r="B15" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A15, " "))</f>
+        <f t="shared" si="0"/>
         <v>106</v>
       </c>
       <c r="C15" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A15, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>employno</v>
       </c>
       <c r="D15" s="10" t="s">
@@ -2784,11 +2798,11 @@
         <v>334</v>
       </c>
       <c r="B16" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A16, " "))</f>
+        <f t="shared" si="0"/>
         <v>107</v>
       </c>
       <c r="C16" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A16, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>employno</v>
       </c>
       <c r="D16" s="10" t="s">
@@ -2803,11 +2817,11 @@
         <v>347</v>
       </c>
       <c r="B17" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A17, " "))</f>
+        <f t="shared" si="0"/>
         <v>117</v>
       </c>
       <c r="C17" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A17, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>IRFAS</v>
       </c>
       <c r="D17" s="10" t="s">
@@ -2822,11 +2836,11 @@
         <v>350</v>
       </c>
       <c r="B18" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A18, " "))</f>
+        <f t="shared" si="0"/>
         <v>118</v>
       </c>
       <c r="C18" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A18, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>IRRELFAS</v>
       </c>
       <c r="D18" s="10" t="s">
@@ -2841,14 +2855,14 @@
         <v>335</v>
       </c>
       <c r="B19" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A19, " "))</f>
+        <f t="shared" si="0"/>
         <v>108</v>
       </c>
       <c r="C19" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A19, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>talkfather</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="11" t="s">
         <v>483</v>
       </c>
       <c r="E19" t="s">
@@ -2860,14 +2874,14 @@
         <v>336</v>
       </c>
       <c r="B20" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A20, " "))</f>
+        <f t="shared" si="0"/>
         <v>109</v>
       </c>
       <c r="C20" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A20, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>talkstepfa</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="11" t="s">
         <v>483</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -2879,14 +2893,14 @@
         <v>337</v>
       </c>
       <c r="B21" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A21, " "))</f>
+        <f t="shared" si="0"/>
         <v>110</v>
       </c>
       <c r="C21" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A21, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>talkmother</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="11" t="s">
         <v>483</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -2898,14 +2912,14 @@
         <v>338</v>
       </c>
       <c r="B22" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A22, " "))</f>
+        <f t="shared" si="0"/>
         <v>111</v>
       </c>
       <c r="C22" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A22, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>talkstepmo</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="11" t="s">
         <v>483</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -2917,14 +2931,14 @@
         <v>339</v>
       </c>
       <c r="B23" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A23, " "))</f>
+        <f t="shared" si="0"/>
         <v>112</v>
       </c>
       <c r="C23" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A23, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>famhelp</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="11" t="s">
         <v>483</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -2936,14 +2950,14 @@
         <v>340</v>
       </c>
       <c r="B24" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A24, " "))</f>
+        <f t="shared" si="0"/>
         <v>113</v>
       </c>
       <c r="C24" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A24, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>famsup</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="11" t="s">
         <v>483</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -2955,14 +2969,14 @@
         <v>342</v>
       </c>
       <c r="B25" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A25, " "))</f>
+        <f t="shared" si="0"/>
         <v>114</v>
       </c>
       <c r="C25" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A25, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>famtalk</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="11" t="s">
         <v>483</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -2974,14 +2988,14 @@
         <v>344</v>
       </c>
       <c r="B26" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A26, " "))</f>
+        <f t="shared" si="0"/>
         <v>115</v>
       </c>
       <c r="C26" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A26, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>famdec</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="11" t="s">
         <v>483</v>
       </c>
       <c r="E26" s="3" t="s">
@@ -2993,14 +3007,14 @@
         <v>249</v>
       </c>
       <c r="B27" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A27, " "))</f>
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="C27" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A27, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>emconlfr</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="12" t="s">
         <v>446</v>
       </c>
       <c r="E27" t="s">
@@ -3012,14 +3026,14 @@
         <v>250</v>
       </c>
       <c r="B28" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A28, " "))</f>
+        <f t="shared" si="0"/>
         <v>76</v>
       </c>
       <c r="C28" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A28, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>emconlfr</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="12" t="s">
         <v>446</v>
       </c>
       <c r="E28" t="s">
@@ -3031,14 +3045,14 @@
         <v>253</v>
       </c>
       <c r="B29" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A29, " "))</f>
+        <f t="shared" si="0"/>
         <v>77</v>
       </c>
       <c r="C29" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A29, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>emconlfr</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="12" t="s">
         <v>446</v>
       </c>
       <c r="E29" t="s">
@@ -3050,14 +3064,14 @@
         <v>254</v>
       </c>
       <c r="B30" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A30, " "))</f>
+        <f t="shared" si="0"/>
         <v>78</v>
       </c>
       <c r="C30" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A30, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>emconlfr</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="12" t="s">
         <v>446</v>
       </c>
       <c r="E30" t="s">
@@ -3069,14 +3083,14 @@
         <v>255</v>
       </c>
       <c r="B31" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A31, " "))</f>
+        <f t="shared" si="0"/>
         <v>79</v>
       </c>
       <c r="C31" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A31, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>emconlpr</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="12" t="s">
         <v>446</v>
       </c>
       <c r="E31" t="s">
@@ -3088,14 +3102,14 @@
         <v>256</v>
       </c>
       <c r="B32" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A32, " "))</f>
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="C32" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A32, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>emconlpr</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="12" t="s">
         <v>446</v>
       </c>
       <c r="E32" t="s">
@@ -3107,14 +3121,14 @@
         <v>259</v>
       </c>
       <c r="B33" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A33, " "))</f>
+        <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="C33" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A33, " "), " ")</f>
+        <f t="shared" si="1"/>
         <v>emconlpr</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="12" t="s">
         <v>446</v>
       </c>
       <c r="E33" t="s">
@@ -3126,11 +3140,11 @@
         <v>241</v>
       </c>
       <c r="B34" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A34, " "))</f>
+        <f t="shared" ref="B34:B65" si="2">INT(_xlfn.TEXTBEFORE(A34, " "))</f>
         <v>71</v>
       </c>
       <c r="C34" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A34, " "), " ")</f>
+        <f t="shared" ref="C34:C65" si="3">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A34, " "), " ")</f>
         <v>friendhelp</v>
       </c>
       <c r="D34" s="8" t="s">
@@ -3145,11 +3159,11 @@
         <v>242</v>
       </c>
       <c r="B35" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A35, " "))</f>
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="C35" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A35, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>friendco</v>
       </c>
       <c r="D35" s="8" t="s">
@@ -3164,11 +3178,11 @@
         <v>244</v>
       </c>
       <c r="B36" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A36, " "))</f>
+        <f t="shared" si="2"/>
         <v>73</v>
       </c>
       <c r="C36" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A36, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>friendsh</v>
       </c>
       <c r="D36" s="8" t="s">
@@ -3183,11 +3197,11 @@
         <v>246</v>
       </c>
       <c r="B37" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A37, " "))</f>
+        <f t="shared" si="2"/>
         <v>74</v>
       </c>
       <c r="C37" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A37, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>friendtalk</v>
       </c>
       <c r="D37" s="8" t="s">
@@ -3202,14 +3216,14 @@
         <v>175</v>
       </c>
       <c r="B38" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A38, " "))</f>
+        <f t="shared" si="2"/>
         <v>37</v>
       </c>
       <c r="C38" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A38, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>physact60</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="13" t="s">
         <v>403</v>
       </c>
       <c r="E38" t="s">
@@ -3221,14 +3235,14 @@
         <v>180</v>
       </c>
       <c r="B39" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A39, " "))</f>
+        <f t="shared" si="2"/>
         <v>38</v>
       </c>
       <c r="C39" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A39, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>breakfas</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="13" t="s">
         <v>403</v>
       </c>
       <c r="E39" t="s">
@@ -3240,14 +3254,14 @@
         <v>184</v>
       </c>
       <c r="B40" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A40, " "))</f>
+        <f t="shared" si="2"/>
         <v>39</v>
       </c>
       <c r="C40" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A40, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>breakfas</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="13" t="s">
         <v>403</v>
       </c>
       <c r="E40" t="s">
@@ -3259,14 +3273,14 @@
         <v>185</v>
       </c>
       <c r="B41" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A41, " "))</f>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="C41" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A41, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>fruits_2</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="13" t="s">
         <v>403</v>
       </c>
       <c r="E41" t="s">
@@ -3278,14 +3292,14 @@
         <v>186</v>
       </c>
       <c r="B42" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A42, " "))</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="C42" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A42, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>vegetabl</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="13" t="s">
         <v>403</v>
       </c>
       <c r="E42" t="s">
@@ -3297,14 +3311,14 @@
         <v>187</v>
       </c>
       <c r="B43" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A43, " "))</f>
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
       <c r="C43" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A43, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>sweets_2</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="13" t="s">
         <v>403</v>
       </c>
       <c r="E43" t="s">
@@ -3316,14 +3330,14 @@
         <v>188</v>
       </c>
       <c r="B44" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A44, " "))</f>
+        <f t="shared" si="2"/>
         <v>43</v>
       </c>
       <c r="C44" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A44, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>softdrin</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" s="13" t="s">
         <v>403</v>
       </c>
       <c r="E44" t="s">
@@ -3335,14 +3349,14 @@
         <v>191</v>
       </c>
       <c r="B45" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A45, " "))</f>
+        <f t="shared" si="2"/>
         <v>45</v>
       </c>
       <c r="C45" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A45, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>toothbr</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="13" t="s">
         <v>403</v>
       </c>
       <c r="E45" t="s">
@@ -3354,14 +3368,14 @@
         <v>192</v>
       </c>
       <c r="B46" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A46, " "))</f>
+        <f t="shared" si="2"/>
         <v>46</v>
       </c>
       <c r="C46" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>timeexe</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D46" s="13" t="s">
         <v>403</v>
       </c>
       <c r="E46" t="s">
@@ -3373,11 +3387,11 @@
         <v>165</v>
       </c>
       <c r="B47" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A47, " "))</f>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="C47" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>lifesat</v>
       </c>
       <c r="D47" s="9" t="s">
@@ -3392,11 +3406,11 @@
         <v>169</v>
       </c>
       <c r="B48" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A48, " "))</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="C48" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A48, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>feellow</v>
       </c>
       <c r="D48" s="9" t="s">
@@ -3411,11 +3425,11 @@
         <v>170</v>
       </c>
       <c r="B49" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A49, " "))</f>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="C49" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A49, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>irritable</v>
       </c>
       <c r="D49" s="9" t="s">
@@ -3430,11 +3444,11 @@
         <v>171</v>
       </c>
       <c r="B50" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A50, " "))</f>
+        <f t="shared" si="2"/>
         <v>33</v>
       </c>
       <c r="C50" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A50, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>nervous</v>
       </c>
       <c r="D50" s="9" t="s">
@@ -3449,11 +3463,11 @@
         <v>172</v>
       </c>
       <c r="B51" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A51, " "))</f>
+        <f t="shared" si="2"/>
         <v>34</v>
       </c>
       <c r="C51" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A51, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>sleepdif</v>
       </c>
       <c r="D51" s="9" t="s">
@@ -3468,11 +3482,11 @@
         <v>173</v>
       </c>
       <c r="B52" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A52, " "))</f>
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="C52" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A52, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>dizzy</v>
       </c>
       <c r="D52" s="9" t="s">
@@ -3487,11 +3501,11 @@
         <v>174</v>
       </c>
       <c r="B53" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A53, " "))</f>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="C53" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A53, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>thinkbody</v>
       </c>
       <c r="D53" s="9" t="s">
@@ -3506,11 +3520,11 @@
         <v>164</v>
       </c>
       <c r="B54" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A54, " "))</f>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="C54" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A54, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>health</v>
       </c>
       <c r="D54" s="7" t="s">
@@ -3525,11 +3539,11 @@
         <v>166</v>
       </c>
       <c r="B55" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A55, " "))</f>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="C55" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A55, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>headache</v>
       </c>
       <c r="D55" s="7" t="s">
@@ -3544,11 +3558,11 @@
         <v>167</v>
       </c>
       <c r="B56" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A56, " "))</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="C56" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A56, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>stomacha</v>
       </c>
       <c r="D56" s="7" t="s">
@@ -3563,11 +3577,11 @@
         <v>168</v>
       </c>
       <c r="B57" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A57, " "))</f>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="C57" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A57, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>backache</v>
       </c>
       <c r="D57" s="7" t="s">
@@ -3582,11 +3596,11 @@
         <v>238</v>
       </c>
       <c r="B58" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A58, " "))</f>
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
       <c r="C58" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A58, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>injured12m</v>
       </c>
       <c r="D58" s="7" t="s">
@@ -3601,14 +3615,14 @@
         <v>149</v>
       </c>
       <c r="B59" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A59, " "))</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="C59" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A59, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>fasfamcar</v>
       </c>
-      <c r="D59" s="16" t="s">
+      <c r="D59" s="14" t="s">
         <v>384</v>
       </c>
       <c r="E59" t="s">
@@ -3620,14 +3634,14 @@
         <v>151</v>
       </c>
       <c r="B60" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A60, " "))</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="C60" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A60, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>fasbedroom</v>
       </c>
-      <c r="D60" s="16" t="s">
+      <c r="D60" s="14" t="s">
         <v>384</v>
       </c>
       <c r="E60" t="s">
@@ -3639,14 +3653,14 @@
         <v>153</v>
       </c>
       <c r="B61" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A61, " "))</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="C61" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A61, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>fascompu</v>
       </c>
-      <c r="D61" s="16" t="s">
+      <c r="D61" s="14" t="s">
         <v>384</v>
       </c>
       <c r="E61" t="s">
@@ -3658,14 +3672,14 @@
         <v>157</v>
       </c>
       <c r="B62" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A62, " "))</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="C62" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A62, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>fasbathr</v>
       </c>
-      <c r="D62" s="16" t="s">
+      <c r="D62" s="14" t="s">
         <v>384</v>
       </c>
       <c r="E62" t="s">
@@ -3677,14 +3691,14 @@
         <v>159</v>
       </c>
       <c r="B63" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A63, " "))</f>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="C63" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A63, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>fasdishw</v>
       </c>
-      <c r="D63" s="16" t="s">
+      <c r="D63" s="14" t="s">
         <v>384</v>
       </c>
       <c r="E63" t="s">
@@ -3696,14 +3710,14 @@
         <v>161</v>
       </c>
       <c r="B64" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A64, " "))</f>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="C64" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A64, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>fasholid</v>
       </c>
-      <c r="D64" s="16" t="s">
+      <c r="D64" s="14" t="s">
         <v>384</v>
       </c>
       <c r="E64" t="s">
@@ -3715,14 +3729,14 @@
         <v>189</v>
       </c>
       <c r="B65" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A65, " "))</f>
+        <f t="shared" si="2"/>
         <v>44</v>
       </c>
       <c r="C65" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A65, " "), " ")</f>
+        <f t="shared" si="3"/>
         <v>fmeal</v>
       </c>
-      <c r="D65" s="16" t="s">
+      <c r="D65" s="14" t="s">
         <v>384</v>
       </c>
       <c r="E65" t="s">
@@ -3734,14 +3748,14 @@
         <v>126</v>
       </c>
       <c r="B66" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A66, " "))</f>
+        <f t="shared" ref="B66:B97" si="4">INT(_xlfn.TEXTBEFORE(A66, " "))</f>
         <v>1</v>
       </c>
       <c r="C66" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A66, " "), " ")</f>
+        <f t="shared" ref="C66:C97" si="5">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A66, " "), " ")</f>
         <v>HBSC</v>
       </c>
-      <c r="D66" s="17" t="s">
+      <c r="D66" s="15" t="s">
         <v>123</v>
       </c>
       <c r="E66" t="s">
@@ -3753,14 +3767,14 @@
         <v>127</v>
       </c>
       <c r="B67" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A67, " "))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="C67" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A67, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>seqno_int</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="D67" s="15" t="s">
         <v>123</v>
       </c>
       <c r="E67" t="s">
@@ -3772,14 +3786,14 @@
         <v>139</v>
       </c>
       <c r="B68" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A68, " "))</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="C68" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A68, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>weight</v>
       </c>
-      <c r="D68" s="18" t="s">
+      <c r="D68" s="16" t="s">
         <v>370</v>
       </c>
       <c r="E68" t="s">
@@ -3791,14 +3805,14 @@
         <v>140</v>
       </c>
       <c r="B69" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A69, " "))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="C69" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A69, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>adm</v>
       </c>
-      <c r="D69" s="18" t="s">
+      <c r="D69" s="16" t="s">
         <v>370</v>
       </c>
       <c r="E69" t="s">
@@ -3810,14 +3824,14 @@
         <v>141</v>
       </c>
       <c r="B70" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A70, " "))</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="C70" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A70, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>month</v>
       </c>
-      <c r="D70" s="18" t="s">
+      <c r="D70" s="16" t="s">
         <v>370</v>
       </c>
       <c r="E70" t="s">
@@ -3829,14 +3843,14 @@
         <v>142</v>
       </c>
       <c r="B71" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A71, " "))</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="C71" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A71, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>year</v>
       </c>
-      <c r="D71" s="18" t="s">
+      <c r="D71" s="16" t="s">
         <v>370</v>
       </c>
       <c r="E71" t="s">
@@ -3848,14 +3862,14 @@
         <v>316</v>
       </c>
       <c r="B72" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A72, " "))</f>
+        <f t="shared" si="4"/>
         <v>96</v>
       </c>
       <c r="C72" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A72, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>countryb</v>
       </c>
-      <c r="D72" s="18" t="s">
+      <c r="D72" s="16" t="s">
         <v>370</v>
       </c>
       <c r="E72" t="s">
@@ -3867,14 +3881,14 @@
         <v>319</v>
       </c>
       <c r="B73" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A73, " "))</f>
+        <f t="shared" si="4"/>
         <v>97</v>
       </c>
       <c r="C73" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A73, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>countryb</v>
       </c>
-      <c r="D73" s="18" t="s">
+      <c r="D73" s="16" t="s">
         <v>370</v>
       </c>
       <c r="E73" t="s">
@@ -3886,14 +3900,14 @@
         <v>130</v>
       </c>
       <c r="B74" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A74, " "))</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="C74" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A74, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>cluster</v>
       </c>
-      <c r="D74" s="19" t="s">
+      <c r="D74" s="17" t="s">
         <v>363</v>
       </c>
       <c r="E74" t="s">
@@ -3905,14 +3919,14 @@
         <v>133</v>
       </c>
       <c r="B75" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A75, " "))</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="C75" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A75, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>countryno</v>
       </c>
-      <c r="D75" s="19" t="s">
+      <c r="D75" s="17" t="s">
         <v>363</v>
       </c>
       <c r="E75" t="s">
@@ -3924,14 +3938,14 @@
         <v>134</v>
       </c>
       <c r="B76" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A76, " "))</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="C76" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A76, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>region</v>
       </c>
-      <c r="D76" s="19" t="s">
+      <c r="D76" s="17" t="s">
         <v>363</v>
       </c>
       <c r="E76" t="s">
@@ -3943,14 +3957,14 @@
         <v>135</v>
       </c>
       <c r="B77" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A77, " "))</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="C77" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A77, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>id1</v>
       </c>
-      <c r="D77" s="19" t="s">
+      <c r="D77" s="17" t="s">
         <v>363</v>
       </c>
       <c r="E77" t="s">
@@ -3962,14 +3976,14 @@
         <v>136</v>
       </c>
       <c r="B78" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A78, " "))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="C78" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A78, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>id2</v>
       </c>
-      <c r="D78" s="19" t="s">
+      <c r="D78" s="17" t="s">
         <v>363</v>
       </c>
       <c r="E78" t="s">
@@ -3981,14 +3995,14 @@
         <v>137</v>
       </c>
       <c r="B79" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A79, " "))</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="C79" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A79, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>id3</v>
       </c>
-      <c r="D79" s="19" t="s">
+      <c r="D79" s="17" t="s">
         <v>363</v>
       </c>
       <c r="E79" t="s">
@@ -4000,14 +4014,14 @@
         <v>138</v>
       </c>
       <c r="B80" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A80, " "))</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="C80" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A80, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>id4</v>
       </c>
-      <c r="D80" s="19" t="s">
+      <c r="D80" s="17" t="s">
         <v>363</v>
       </c>
       <c r="E80" t="s">
@@ -4019,14 +4033,14 @@
         <v>209</v>
       </c>
       <c r="B81" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A81, " "))</f>
+        <f t="shared" si="4"/>
         <v>57</v>
       </c>
       <c r="C81" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A81, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>likeschool</v>
       </c>
-      <c r="D81" s="20" t="s">
+      <c r="D81" s="18" t="s">
         <v>422</v>
       </c>
       <c r="E81" t="s">
@@ -4038,14 +4052,14 @@
         <v>211</v>
       </c>
       <c r="B82" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A82, " "))</f>
+        <f t="shared" si="4"/>
         <v>58</v>
       </c>
       <c r="C82" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A82, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>schoolpr</v>
       </c>
-      <c r="D82" s="20" t="s">
+      <c r="D82" s="18" t="s">
         <v>422</v>
       </c>
       <c r="E82" t="s">
@@ -4057,14 +4071,14 @@
         <v>213</v>
       </c>
       <c r="B83" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A83, " "))</f>
+        <f t="shared" si="4"/>
         <v>59</v>
       </c>
       <c r="C83" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A83, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>studtoge</v>
       </c>
-      <c r="D83" s="20" t="s">
+      <c r="D83" s="18" t="s">
         <v>422</v>
       </c>
       <c r="E83" t="s">
@@ -4076,14 +4090,14 @@
         <v>215</v>
       </c>
       <c r="B84" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A84, " "))</f>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="C84" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A84, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>studhelp</v>
       </c>
-      <c r="D84" s="20" t="s">
+      <c r="D84" s="18" t="s">
         <v>422</v>
       </c>
       <c r="E84" t="s">
@@ -4095,14 +4109,14 @@
         <v>217</v>
       </c>
       <c r="B85" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A85, " "))</f>
+        <f t="shared" si="4"/>
         <v>61</v>
       </c>
       <c r="C85" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A85, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>studaccept</v>
       </c>
-      <c r="D85" s="20" t="s">
+      <c r="D85" s="18" t="s">
         <v>422</v>
       </c>
       <c r="E85" t="s">
@@ -4114,14 +4128,14 @@
         <v>218</v>
       </c>
       <c r="B86" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A86, " "))</f>
+        <f t="shared" si="4"/>
         <v>62</v>
       </c>
       <c r="C86" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A86, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>teachera</v>
       </c>
-      <c r="D86" s="20" t="s">
+      <c r="D86" s="18" t="s">
         <v>422</v>
       </c>
       <c r="E86" t="s">
@@ -4133,14 +4147,14 @@
         <v>219</v>
       </c>
       <c r="B87" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A87, " "))</f>
+        <f t="shared" si="4"/>
         <v>63</v>
       </c>
       <c r="C87" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A87, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>teacherc</v>
       </c>
-      <c r="D87" s="20" t="s">
+      <c r="D87" s="18" t="s">
         <v>422</v>
       </c>
       <c r="E87" t="s">
@@ -4152,14 +4166,14 @@
         <v>221</v>
       </c>
       <c r="B88" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A88, " "))</f>
+        <f t="shared" si="4"/>
         <v>64</v>
       </c>
       <c r="C88" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A88, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>teachert</v>
       </c>
-      <c r="D88" s="20" t="s">
+      <c r="D88" s="18" t="s">
         <v>422</v>
       </c>
       <c r="E88" t="s">
@@ -4171,14 +4185,14 @@
         <v>261</v>
       </c>
       <c r="B89" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A89, " "))</f>
+        <f t="shared" si="4"/>
         <v>82</v>
       </c>
       <c r="C89" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A89, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>emcsocmed1</v>
       </c>
-      <c r="D89" s="21" t="s">
+      <c r="D89" s="19" t="s">
         <v>453</v>
       </c>
       <c r="E89" t="s">
@@ -4190,14 +4204,14 @@
         <v>266</v>
       </c>
       <c r="B90" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A90, " "))</f>
+        <f t="shared" si="4"/>
         <v>83</v>
       </c>
       <c r="C90" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A90, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>emcsocmed2</v>
       </c>
-      <c r="D90" s="21" t="s">
+      <c r="D90" s="19" t="s">
         <v>453</v>
       </c>
       <c r="E90" t="s">
@@ -4209,14 +4223,14 @@
         <v>271</v>
       </c>
       <c r="B91" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A91, " "))</f>
+        <f t="shared" si="4"/>
         <v>84</v>
       </c>
       <c r="C91" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A91, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>emcsocmed3</v>
       </c>
-      <c r="D91" s="21" t="s">
+      <c r="D91" s="19" t="s">
         <v>453</v>
       </c>
       <c r="E91" t="s">
@@ -4228,14 +4242,14 @@
         <v>273</v>
       </c>
       <c r="B92" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A92, " "))</f>
+        <f t="shared" si="4"/>
         <v>85</v>
       </c>
       <c r="C92" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A92, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>emcsocmed4</v>
       </c>
-      <c r="D92" s="21" t="s">
+      <c r="D92" s="19" t="s">
         <v>453</v>
       </c>
       <c r="E92" t="s">
@@ -4247,14 +4261,14 @@
         <v>277</v>
       </c>
       <c r="B93" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A93, " "))</f>
+        <f t="shared" si="4"/>
         <v>86</v>
       </c>
       <c r="C93" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A93, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>emcsocmed5</v>
       </c>
-      <c r="D93" s="21" t="s">
+      <c r="D93" s="19" t="s">
         <v>453</v>
       </c>
       <c r="E93" t="s">
@@ -4266,14 +4280,14 @@
         <v>282</v>
       </c>
       <c r="B94" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A94, " "))</f>
+        <f t="shared" si="4"/>
         <v>87</v>
       </c>
       <c r="C94" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A94, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>emcsocmed6</v>
       </c>
-      <c r="D94" s="21" t="s">
+      <c r="D94" s="19" t="s">
         <v>453</v>
       </c>
       <c r="E94" t="s">
@@ -4285,14 +4299,14 @@
         <v>286</v>
       </c>
       <c r="B95" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A95, " "))</f>
+        <f t="shared" si="4"/>
         <v>88</v>
       </c>
       <c r="C95" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A95, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>emcsocmed7</v>
       </c>
-      <c r="D95" s="21" t="s">
+      <c r="D95" s="19" t="s">
         <v>453</v>
       </c>
       <c r="E95" t="s">
@@ -4304,14 +4318,14 @@
         <v>291</v>
       </c>
       <c r="B96" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A96, " "))</f>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="C96" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A96, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>emcsocmed8</v>
       </c>
-      <c r="D96" s="21" t="s">
+      <c r="D96" s="19" t="s">
         <v>453</v>
       </c>
       <c r="E96" t="s">
@@ -4323,14 +4337,14 @@
         <v>295</v>
       </c>
       <c r="B97" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A97, " "))</f>
+        <f t="shared" si="4"/>
         <v>90</v>
       </c>
       <c r="C97" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A97, " "), " ")</f>
+        <f t="shared" si="5"/>
         <v>emcsocmed9</v>
       </c>
-      <c r="D97" s="21" t="s">
+      <c r="D97" s="19" t="s">
         <v>453</v>
       </c>
       <c r="E97" t="s">
@@ -4342,14 +4356,14 @@
         <v>143</v>
       </c>
       <c r="B98" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A98, " "))</f>
+        <f t="shared" ref="B98:B129" si="6">INT(_xlfn.TEXTBEFORE(A98, " "))</f>
         <v>14</v>
       </c>
       <c r="C98" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A98, " "), " ")</f>
+        <f t="shared" ref="C98:C115" si="7">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A98, " "), " ")</f>
         <v>age</v>
       </c>
-      <c r="D98" s="22" t="s">
+      <c r="D98" s="20" t="s">
         <v>493</v>
       </c>
       <c r="E98" t="s">
@@ -4361,14 +4375,14 @@
         <v>144</v>
       </c>
       <c r="B99" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A99, " "))</f>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="C99" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A99, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>agecat</v>
       </c>
-      <c r="D99" s="22" t="s">
+      <c r="D99" s="20" t="s">
         <v>493</v>
       </c>
       <c r="E99" t="s">
@@ -4380,14 +4394,14 @@
         <v>145</v>
       </c>
       <c r="B100" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A100, " "))</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="C100" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A100, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>sex</v>
       </c>
-      <c r="D100" s="22" t="s">
+      <c r="D100" s="20" t="s">
         <v>493</v>
       </c>
       <c r="E100" t="s">
@@ -4399,14 +4413,14 @@
         <v>146</v>
       </c>
       <c r="B101" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A101, " "))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="C101" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A101, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>grade</v>
       </c>
-      <c r="D101" s="22" t="s">
+      <c r="D101" s="20" t="s">
         <v>493</v>
       </c>
       <c r="E101" t="s">
@@ -4418,14 +4432,14 @@
         <v>147</v>
       </c>
       <c r="B102" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A102, " "))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="C102" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A102, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>monthbirth</v>
       </c>
-      <c r="D102" s="22" t="s">
+      <c r="D102" s="20" t="s">
         <v>493</v>
       </c>
       <c r="E102" t="s">
@@ -4437,14 +4451,14 @@
         <v>148</v>
       </c>
       <c r="B103" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A103, " "))</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="C103" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A103, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>yearbirth</v>
       </c>
-      <c r="D103" s="22" t="s">
+      <c r="D103" s="20" t="s">
         <v>493</v>
       </c>
       <c r="E103" t="s">
@@ -4456,14 +4470,14 @@
         <v>206</v>
       </c>
       <c r="B104" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A104, " "))</f>
+        <f t="shared" si="6"/>
         <v>55</v>
       </c>
       <c r="C104" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A104, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>bodyweight</v>
       </c>
-      <c r="D104" s="22" t="s">
+      <c r="D104" s="20" t="s">
         <v>493</v>
       </c>
       <c r="E104" t="s">
@@ -4475,14 +4489,14 @@
         <v>208</v>
       </c>
       <c r="B105" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A105, " "))</f>
+        <f t="shared" si="6"/>
         <v>56</v>
       </c>
       <c r="C105" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A105, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>bodyheight</v>
       </c>
-      <c r="D105" s="22" t="s">
+      <c r="D105" s="20" t="s">
         <v>493</v>
       </c>
       <c r="E105" t="s">
@@ -4494,14 +4508,14 @@
         <v>315</v>
       </c>
       <c r="B106" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A106, " "))</f>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="C106" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A106, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>countryb</v>
       </c>
-      <c r="D106" s="22" t="s">
+      <c r="D106" s="20" t="s">
         <v>493</v>
       </c>
       <c r="E106" t="s">
@@ -4513,14 +4527,14 @@
         <v>346</v>
       </c>
       <c r="B107" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A107, " "))</f>
+        <f t="shared" si="6"/>
         <v>116</v>
       </c>
       <c r="C107" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A107, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>MBMI</v>
       </c>
-      <c r="D107" s="22" t="s">
+      <c r="D107" s="20" t="s">
         <v>493</v>
       </c>
       <c r="E107" t="s">
@@ -4532,14 +4546,14 @@
         <v>352</v>
       </c>
       <c r="B108" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A108, " "))</f>
+        <f t="shared" si="6"/>
         <v>119</v>
       </c>
       <c r="C108" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A108, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>IOTF4</v>
       </c>
-      <c r="D108" s="23" t="s">
+      <c r="D108" s="21" t="s">
         <v>493</v>
       </c>
       <c r="E108" t="s">
@@ -4551,14 +4565,14 @@
         <v>353</v>
       </c>
       <c r="B109" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A109, " "))</f>
+        <f t="shared" si="6"/>
         <v>120</v>
       </c>
       <c r="C109" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A109, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>oweight_</v>
       </c>
-      <c r="D109" s="23" t="s">
+      <c r="D109" s="21" t="s">
         <v>493</v>
       </c>
       <c r="E109" t="s">
@@ -4570,14 +4584,14 @@
         <v>198</v>
       </c>
       <c r="B110" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A110, " "))</f>
+        <f t="shared" si="6"/>
         <v>47</v>
       </c>
       <c r="C110" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A110, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>smokltm</v>
       </c>
-      <c r="D110" s="24" t="s">
+      <c r="D110" s="22" t="s">
         <v>411</v>
       </c>
       <c r="E110" t="s">
@@ -4589,14 +4603,14 @@
         <v>199</v>
       </c>
       <c r="B111" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A111, " "))</f>
+        <f t="shared" si="6"/>
         <v>48</v>
       </c>
       <c r="C111" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A111, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>smok30d_2</v>
       </c>
-      <c r="D111" s="24" t="s">
+      <c r="D111" s="22" t="s">
         <v>411</v>
       </c>
       <c r="E111" t="s">
@@ -4608,14 +4622,14 @@
         <v>200</v>
       </c>
       <c r="B112" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A112, " "))</f>
+        <f t="shared" si="6"/>
         <v>49</v>
       </c>
       <c r="C112" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A112, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>alcltm</v>
       </c>
-      <c r="D112" s="24" t="s">
+      <c r="D112" s="22" t="s">
         <v>411</v>
       </c>
       <c r="E112" t="s">
@@ -4627,14 +4641,14 @@
         <v>201</v>
       </c>
       <c r="B113" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A113, " "))</f>
+        <f t="shared" si="6"/>
         <v>50</v>
       </c>
       <c r="C113" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A113, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>alc30d_2</v>
       </c>
-      <c r="D113" s="24" t="s">
+      <c r="D113" s="22" t="s">
         <v>411</v>
       </c>
       <c r="E113" t="s">
@@ -4646,14 +4660,14 @@
         <v>202</v>
       </c>
       <c r="B114" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A114, " "))</f>
+        <f t="shared" si="6"/>
         <v>51</v>
       </c>
       <c r="C114" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A114, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>drunkltm</v>
       </c>
-      <c r="D114" s="24" t="s">
+      <c r="D114" s="22" t="s">
         <v>411</v>
       </c>
       <c r="E114" t="s">
@@ -4665,14 +4679,14 @@
         <v>203</v>
       </c>
       <c r="B115" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A115, " "))</f>
+        <f t="shared" si="6"/>
         <v>52</v>
       </c>
       <c r="C115" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A115, " "), " ")</f>
+        <f t="shared" si="7"/>
         <v>drunk30d</v>
       </c>
-      <c r="D115" s="24" t="s">
+      <c r="D115" s="22" t="s">
         <v>411</v>
       </c>
       <c r="E115" t="s">
@@ -4684,13 +4698,13 @@
         <v>204</v>
       </c>
       <c r="B116" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A116, " "))</f>
+        <f t="shared" si="6"/>
         <v>53</v>
       </c>
       <c r="C116" t="s">
         <v>52</v>
       </c>
-      <c r="D116" s="24" t="s">
+      <c r="D116" s="22" t="s">
         <v>411</v>
       </c>
       <c r="E116" t="s">
@@ -4702,13 +4716,13 @@
         <v>205</v>
       </c>
       <c r="B117" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A117, " "))</f>
+        <f t="shared" si="6"/>
         <v>54</v>
       </c>
       <c r="C117" t="s">
         <v>53</v>
       </c>
-      <c r="D117" s="24" t="s">
+      <c r="D117" s="22" t="s">
         <v>411</v>
       </c>
       <c r="E117" t="s">
@@ -4720,14 +4734,14 @@
         <v>300</v>
       </c>
       <c r="B118" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A118, " "))</f>
+        <f t="shared" si="6"/>
         <v>91</v>
       </c>
       <c r="C118" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A118, " "), " ")</f>
         <v>hadsex</v>
       </c>
-      <c r="D118" s="24" t="s">
+      <c r="D118" s="22" t="s">
         <v>411</v>
       </c>
       <c r="E118" t="s">
@@ -4739,14 +4753,14 @@
         <v>304</v>
       </c>
       <c r="B119" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A119, " "))</f>
+        <f t="shared" si="6"/>
         <v>92</v>
       </c>
       <c r="C119" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A119, " "), " ")</f>
         <v>agesex</v>
       </c>
-      <c r="D119" s="24" t="s">
+      <c r="D119" s="22" t="s">
         <v>411</v>
       </c>
       <c r="E119" t="s">
@@ -4758,14 +4772,14 @@
         <v>308</v>
       </c>
       <c r="B120" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A120, " "))</f>
+        <f t="shared" si="6"/>
         <v>93</v>
       </c>
       <c r="C120" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A120, " "), " ")</f>
         <v>contrace</v>
       </c>
-      <c r="D120" s="24" t="s">
+      <c r="D120" s="22" t="s">
         <v>411</v>
       </c>
       <c r="E120" t="s">
@@ -4777,14 +4791,14 @@
         <v>310</v>
       </c>
       <c r="B121" s="2">
-        <f>INT(_xlfn.TEXTBEFORE(A121, " "))</f>
+        <f t="shared" si="6"/>
         <v>94</v>
       </c>
       <c r="C121" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A121, " "), " ")</f>
         <v>contrace</v>
       </c>
-      <c r="D121" s="24" t="s">
+      <c r="D121" s="22" t="s">
         <v>411</v>
       </c>
       <c r="E121" t="s">
